--- a/AAII_Financials/Quarterly/SHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>SHG</t>
   </si>
@@ -656,273 +656,279 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2750900</v>
+        <v>6639100</v>
       </c>
       <c r="E8" s="3">
+        <v>6763500</v>
+      </c>
+      <c r="F8" s="3">
         <v>2566100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2842900</v>
       </c>
-      <c r="G8" s="3">
-        <v>3026100</v>
-      </c>
       <c r="H8" s="3">
-        <v>2667300</v>
+        <v>7187200</v>
       </c>
       <c r="I8" s="3">
+        <v>4080900</v>
+      </c>
+      <c r="J8" s="3">
         <v>2061700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2939700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2764000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2899800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2624900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2678100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2761600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2741000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4622300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3800000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3473100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3198500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2930100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2768700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2702300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2606800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2638000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2766100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2891700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3243500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3353300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3542100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3466400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3497400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3024500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2816100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2801000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2655000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2731700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2636600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2533700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2537200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2578000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2529700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1043,53 +1049,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2750900</v>
+        <v>6639100</v>
       </c>
       <c r="E10" s="3">
+        <v>6763500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2566100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2842900</v>
       </c>
-      <c r="G10" s="3">
-        <v>3026100</v>
-      </c>
       <c r="H10" s="3">
-        <v>2667300</v>
+        <v>7187200</v>
       </c>
       <c r="I10" s="3">
+        <v>4080900</v>
+      </c>
+      <c r="J10" s="3">
         <v>2061700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2939700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2764000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2899800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2624900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2678100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2761600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2741000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1165,8 +1174,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,8 +1221,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1331,8 +1344,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1453,52 +1469,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>195900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>178700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>161700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1575,130 +1594,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E15" s="3">
         <v>205700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>113500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>222200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>241600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>225200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>114200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>253000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>224200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>227900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>125000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>222300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>223300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>215300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-128200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-116300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-120800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-122600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-130400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-118200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-115400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-118700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-113100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-113700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-116300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-129300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-126300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-130500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-126800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-127000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-51600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-50400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-51500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-50700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-52100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-51500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-52000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-57100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-54000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-55700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,252 +1763,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1335600</v>
+        <v>3662800</v>
       </c>
       <c r="E17" s="3">
+        <v>2457800</v>
+      </c>
+      <c r="F17" s="3">
         <v>1624200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1451500</v>
       </c>
-      <c r="G17" s="3">
-        <v>1537800</v>
-      </c>
       <c r="H17" s="3">
-        <v>1347100</v>
+        <v>2653800</v>
       </c>
       <c r="I17" s="3">
+        <v>2184200</v>
+      </c>
+      <c r="J17" s="3">
         <v>1469500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1516000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1419600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1360800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1746600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1412200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1443400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1394100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2882400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1986400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1750100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1478600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1131100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>881700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>824500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>848300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1033800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>877500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1008200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1412700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1241100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1341400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1355400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1330200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1152900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1056900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1018500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>926000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1247900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1064800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>978800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>928800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1125700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1097800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1415300</v>
+        <v>2976200</v>
       </c>
       <c r="E18" s="3">
+        <v>4305700</v>
+      </c>
+      <c r="F18" s="3">
         <v>941800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1391400</v>
       </c>
-      <c r="G18" s="3">
-        <v>1488300</v>
-      </c>
       <c r="H18" s="3">
-        <v>1320200</v>
+        <v>4533400</v>
       </c>
       <c r="I18" s="3">
+        <v>1896700</v>
+      </c>
+      <c r="J18" s="3">
         <v>592100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1423700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1344400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1538900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>878300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1265900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1318100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1346900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1739900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1813600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1723100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1719900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1798900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1887000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1877800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1758500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1604200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1888600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1883500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1830800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2112200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2200700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2111000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2167200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1871600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1759200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1782400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1729000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1483800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1571800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1555000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1608400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1452300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1431900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2026,252 +2058,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-44000</v>
+        <v>1351500</v>
       </c>
       <c r="E20" s="3">
+        <v>2846400</v>
+      </c>
+      <c r="F20" s="3">
         <v>122000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-42800</v>
-      </c>
       <c r="H20" s="3">
-        <v>-41700</v>
+        <v>3002400</v>
       </c>
       <c r="I20" s="3">
+        <v>534900</v>
+      </c>
+      <c r="J20" s="3">
         <v>6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>79600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>206700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>107800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>84500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-77100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1387300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-202600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-370300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-249400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-728700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-581000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-540900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1097500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-686100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-935800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-758500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1467300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-940100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-866700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-963700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1201600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-814500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-683100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-726000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1289700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-620900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-508200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-433200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-882000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-578500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1821600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1665100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>933300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1610800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1772700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1587100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>700300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1597100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1582300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1560100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>895500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1403700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1535600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1639400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>555400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1793700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1538500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1651100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>685800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1326000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1457100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1377300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>656400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1350000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1092800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1228800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>795600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1414000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1391600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1349200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>737400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1008900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1161100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1060800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>250900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1005400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1100800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1234100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>626000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>910900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2314,8 +2353,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2392,252 +2431,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1624700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1459300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>624000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1388500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1531100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1361900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>407400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1344100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1358100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1332300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>608700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1181400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1312300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1424000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>352600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1611000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1352800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1470500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>498700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1158300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1296800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1217500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>506800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1202500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>947800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1072300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>644800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1260500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1244300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1203500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>669900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>944700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1099400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1003000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>194100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>950800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1175100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>570300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>853400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>432200</v>
+      </c>
+      <c r="E24" s="3">
         <v>375900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>251200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>354800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>365700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>331700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>113600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>334900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>305100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>329400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>164500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>276000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>349000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>339300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>408200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>351800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>388600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>142500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>302000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>338300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>316300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>144600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>304300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>260400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>274700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>170900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>327400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>302300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>324600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>230000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>250100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>273000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>8800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>221800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>253100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>268600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>17300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>203300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2758,252 +2806,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1192500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1083400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>372700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1033700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1165400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1030100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>293700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1009200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1053000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1002900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>444200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>905400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>963300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1084700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>289300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1202800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1081900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>356200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>856400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>958500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>901300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>362100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>898200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>687400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>797600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>473900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>933100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>942100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>878900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>439900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>694600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>796400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>730000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>185300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>729000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>793700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>906500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>553000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>650200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1139400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1037000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>316000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>981800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1102800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>981700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>239300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>958200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>998100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>956700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>387900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>847700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>906700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1027700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>239700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1153100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>959600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1037500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>323600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>809200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>924000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>858800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>332400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>859000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>663200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>758700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>428300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>854700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>860000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>819000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>415700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>677200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>783100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>716600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>182000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>716900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>781100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>891800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>544500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>628400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3124,8 +3181,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3246,8 +3306,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3368,8 +3431,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3490,252 +3556,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>44000</v>
+        <v>-1351500</v>
       </c>
       <c r="E32" s="3">
+        <v>-2846400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-122000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
-        <v>42800</v>
-      </c>
       <c r="H32" s="3">
-        <v>41700</v>
+        <v>-3002400</v>
       </c>
       <c r="I32" s="3">
+        <v>-534900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-79600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-206700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-107800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-84500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>77100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1387300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>202600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>370300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>249400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>728700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>581000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>540900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1097500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>686100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>935800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>758500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1467300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>940100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>866700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>963700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1201600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>814500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>683100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>726000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1289700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>620900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>508200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>433200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>882000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>578500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1175300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1065900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>353700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1013300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1144600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1010600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>274900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>987600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1034500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>983300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>423900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>885500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>940200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1064500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>239700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1153100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>959600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1037500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>323600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>809200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>924000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>858800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>332400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>859000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>663200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>758700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>428300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>854700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>860000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>819000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>415700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>677200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>783100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>716600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>182000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>716900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>781100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>891800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>544500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>628400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3856,257 +3931,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1175300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1065900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>353700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1013300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1144600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1010600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>274900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>987600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1034500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>983300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>423900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>885500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>940200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1064500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>239700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1153100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>959600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1037500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>323600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>809200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>924000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>858800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>332400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>859000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>663200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>758700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>428300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>854700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>860000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>819000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>415700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>677200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>783100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>716600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>182000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>716900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>781100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>891800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>544500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>628400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4149,8 +4233,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4193,296 +4278,303 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31049500</v>
+      </c>
+      <c r="E41" s="3">
         <v>23762500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24439600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30737600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26092600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26060600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23845800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30114500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22184200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22861100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23439800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22821000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16476500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27437900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28109800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>32191600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27223000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25575500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24227200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27077600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24459300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26646600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28788200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27978900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28287400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29019700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26398700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>25746400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24389000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>23054900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>17584700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>15500100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>17801600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>18641300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>22561800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>25566200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>23142700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>26289300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>21519900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>21820800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>153453100</v>
+      </c>
+      <c r="E42" s="3">
         <v>57601200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>57182500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>57420400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>57394700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>54869800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55635200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>61655000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>58085500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57587400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58048000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>54248000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>143791000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>144327700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>140107000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>140177500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>142224600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>144782900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>135728500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>134947100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>129482800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>128003000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>126039800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>126797100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>124832900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>137555400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>136812200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>138254700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>130804300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>128262600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>94181400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>87806500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>90551000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>87816800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>31190300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>31578300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>32256300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>31847000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>29803400</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>31161800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>50700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19086000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>54300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>69200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9275000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13194400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4559,8 +4651,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4603,8 +4698,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4681,53 +4776,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2841300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6298300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2673200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1836000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1550700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4851600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1654000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1557600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1526400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5630000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1397800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43400</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4803,53 +4901,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>184585100</v>
+      </c>
+      <c r="E46" s="3">
         <v>86347700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109701500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92947200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>87900700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>84880900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96332000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96114000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>84099400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>84126000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>102791700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>80899800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>172401000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>171809000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4925,374 +5026,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1575100</v>
+      </c>
+      <c r="E47" s="3">
         <v>90648200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>95461500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>95446100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>97698900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>88611300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>87916300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97932600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>92590400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94320900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>99240000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>92608100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2231800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2261600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2178400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2045600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2077900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2089000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2185300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1944500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1968900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2088900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1966700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2066100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1844600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1707400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1234900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>898800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>739600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>631800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>563900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>618400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>613900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>522200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>555500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>525300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>545200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>465600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>318200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>263800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2632400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2742400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2877100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2832700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2954800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2790100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2814400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3046200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2879600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2953200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3063300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2936300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2957100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3098300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6561300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3154700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3274900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3635400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3541200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3453100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3448400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3420100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3407600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3538100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3675400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4039000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3886100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3655800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3609500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3739100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2922100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2804700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2920600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2856400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3027300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3014800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3040900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3122600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3148900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3076700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3833000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3937200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3705600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4204400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4404900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4116200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3684300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4677000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4483800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4609100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4436700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4632300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4738900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4815700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8711800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4170700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4360300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4369900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4233600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4135100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4128500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4075400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4055700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4263100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4257500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4663300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4724900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5044700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4915000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5118400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3628900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3480700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3623300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3603700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3759300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3717200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3729800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3816300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3803900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3804800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5413,8 +5526,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5535,130 +5651,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39710000</v>
+      </c>
+      <c r="E52" s="3">
         <v>38867600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10271200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35091000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31626500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21612300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5283500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28220900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28560000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27340300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5957200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25817400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23834300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24007200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1051100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1036500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>982900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>508400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>241000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>145500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>152100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>128700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>213200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>173700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>120600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>99800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>208300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>165700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>113700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>233600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>365000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>366000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>425200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>512000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>527900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>451200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>469200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>460300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>581400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>370500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5779,130 +5901,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>542999400</v>
+      </c>
+      <c r="E54" s="3">
         <v>536536300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>544511700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>557332200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>556156800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>506713900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>500771200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>567527700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>528069600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>528118800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>533479900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>512575100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>513990800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>518591300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>498324900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>508239700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>519252000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>513378900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>486114100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>478991400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>469532300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>457865400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>447873200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>455712500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>445330600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>485602400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>469556600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>485849200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>466532100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>467617500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>386064400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>370742500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>380756900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>364298000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>375149000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>378217500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>364241600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>364496400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>356112300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>359087000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5945,8 +6073,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5989,175 +6118,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>307972300</v>
+      </c>
+      <c r="E57" s="3">
         <v>304642200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>331272200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>312474000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>311340400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>285746100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>296848200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>317080200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>292623600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>293860800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>309116000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>286298700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>293017300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>290399700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11340400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>12115300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>15224300</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>11552600</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>9315700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>9289600</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AO57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP57" s="3">
         <v>7619300</v>
       </c>
-      <c r="AP57" s="3" t="s">
+      <c r="AQ57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19354800</v>
+      </c>
+      <c r="E58" s="3">
         <v>21144700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20661800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18480800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20947800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18686800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21024500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23826400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23247000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23116000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24929900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>23147200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14509500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16553000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6233,175 +6366,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4994000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1303700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1667200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>866200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>752700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>519600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1075700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1335600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1464100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1424000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1872000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1223800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7555700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8083300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3865300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>450300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>406900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>701400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3006700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>393200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>386300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>461300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2572500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>330000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>209300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>456500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3439900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>407700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>274200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>463700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3147500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>275800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>176900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>302700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2973800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>358900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>294100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>400000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2806000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>165000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>332321100</v>
+      </c>
+      <c r="E60" s="3">
         <v>327090600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>358425800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>331820900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>333041000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>304952600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>323702600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>342242200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>317334700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>318400800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>340450100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>310669700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>315082500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>315036100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6477,252 +6616,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>119587300</v>
+      </c>
+      <c r="E61" s="3">
         <v>85527300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>91962600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>92389000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>94423600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87381100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>89218100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>96520400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>90921600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>90798700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>92217600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>86398700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>121260900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>123850000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>86799000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>91347900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>90698000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>86671300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>83757300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>80828600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>80206600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>76706600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>77319900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>77710700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>77299800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>86174500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>86283300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>85704500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>89492600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>80450800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>70553200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>70552800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>71684500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>66501100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>60720700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>69513400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>67293600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>63481300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>54355900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>61529000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>49916100</v>
+      </c>
+      <c r="E62" s="3">
         <v>82985300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>51668800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>89493800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>83663100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73776600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47412100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>83555700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>77576500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>76225000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>56528800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>73064300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34647400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36480900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1568700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>898700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>925600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1080700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1045500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1036000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1040000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>968300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1070700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1109800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1088300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>941700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>960300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1211500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1191100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>947100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>552500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>485700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>521800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>455200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>392300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>543400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>526700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>534600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>783400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>928700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6843,8 +6991,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6965,8 +7116,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7087,130 +7241,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>502627900</v>
+      </c>
+      <c r="E66" s="3">
         <v>496151200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>502688700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>514210300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>511678600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>466414600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>460953300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>522783800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>486268200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>485880600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>490047100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>470666100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>471449900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>475799000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>460276000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>472835000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>483266500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>476898400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>450645800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>443617000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>434864000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>424929000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>415261800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>421874300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>413542800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>451772100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>436255400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>451188100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>433039900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>434708800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>356054900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>342149700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>352543600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>337041400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>346268100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>349357900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>336212500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>336331400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>328113600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>331277800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7253,8 +7413,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7375,8 +7536,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7497,8 +7661,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7542,19 +7709,19 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>271100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>263900</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>274700</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>278300</v>
-      </c>
-      <c r="U70" s="3">
-        <v>271100</v>
       </c>
       <c r="V70" s="3">
         <v>271100</v>
@@ -7563,46 +7730,46 @@
         <v>271100</v>
       </c>
       <c r="X70" s="3">
-        <v>267500</v>
+        <v>271100</v>
       </c>
       <c r="Y70" s="3">
         <v>267500</v>
       </c>
       <c r="Z70" s="3">
-        <v>278300</v>
+        <v>267500</v>
       </c>
       <c r="AA70" s="3">
         <v>278300</v>
       </c>
       <c r="AB70" s="3">
+        <v>278300</v>
+      </c>
+      <c r="AC70" s="3">
         <v>303600</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>307200</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>321700</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>318100</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>249400</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>230200</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>222000</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>230200</v>
       </c>
       <c r="AJ70" s="3">
         <v>230200</v>
       </c>
       <c r="AK70" s="3">
-        <v>241200</v>
+        <v>230200</v>
       </c>
       <c r="AL70" s="3">
         <v>241200</v>
@@ -7611,7 +7778,7 @@
         <v>241200</v>
       </c>
       <c r="AN70" s="3">
-        <v>246600</v>
+        <v>241200</v>
       </c>
       <c r="AO70" s="3">
         <v>246600</v>
@@ -7619,8 +7786,11 @@
       <c r="AP70" s="3">
         <v>246600</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>246600</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7741,130 +7911,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34513700</v>
+      </c>
+      <c r="E72" s="3">
         <v>34171900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28954300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29623900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29933800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27294700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26414300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29871200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27754400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27640100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28060200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26929700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26941400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26624300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25472800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>24395200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24383300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23990500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>22906000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22687700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22003300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>20811500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>20555100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21058200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20211100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21454800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21696900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22274000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21183700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21020600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19285900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18198300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18172000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>17391800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18295700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>18113700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>17397100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>16993700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>16776000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>16231500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7985,8 +8161,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8107,8 +8286,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8229,130 +8411,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38809500</v>
+      </c>
+      <c r="E76" s="3">
         <v>38798400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>40151300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41194900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42257100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38581500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37944700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42638200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39794800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40479000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41426700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>39828700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40415900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40417300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37777800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35140900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35710700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>36202100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35197300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35103300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34397200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32668800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>32344000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>33559900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>31509500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>33526700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32994000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>34339400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33174100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32659300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>29779300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>28370900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>27983000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>27026400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>28639700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>28618400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>27787900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>27918300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>27752100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>27562500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8473,257 +8661,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1175300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1065900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>353700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1013300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1144600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1010600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>274900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>987600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1034500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>983300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>423900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>885500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>940200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1064500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>239700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1153100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>959600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1037500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>323600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>809200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>924000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>858800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>332400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>859000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>663200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>758700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>428300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>854700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>860000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>819000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>415700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>677200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>783100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>716600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>182000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>716900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>781100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>891800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>544500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>628400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8766,130 +8963,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E83" s="3">
         <v>173600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>194500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>178200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>182800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>66300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>179600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>178800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>176600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>73700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>150700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>165300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>193100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>212600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>193200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>196000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>190800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>187100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>167700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>160300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>159700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>149600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>147600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>145100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>156400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>150800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>153500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>147200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>145700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>67500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>64200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>57800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>56800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>54500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>54000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>58900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>55700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>57400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9010,8 +9211,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9132,8 +9336,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9254,8 +9461,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9376,8 +9586,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9498,130 +9711,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6546000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9841700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2898400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5741800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7935800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2937900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4752200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7087000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10342500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1280100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4013800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-481400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7368200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1390500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2435200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>677900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1163200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>849600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4789600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-263600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2895300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2601700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-906900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>390700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-187500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1621800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4852300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1298700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1964900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4638800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1423900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1812900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-333800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2105900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-119900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-1615600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>540300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1302000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>717500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9664,130 +9883,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-44300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-40900</v>
-      </c>
       <c r="H91" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-27700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-52000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-66800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-51100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-49800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-295310000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-195675000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-220069000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-232073000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-331256000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-235964000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-41900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-53400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-49300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-80100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-122500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-53000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-27000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-55000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-35500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-35900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-49600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9908,8 +10131,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10030,130 +10256,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-788700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3369300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4022700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1974300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2102900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>354800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-498500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-145500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-106800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>910100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-913300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1625500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-956100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>276100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1061400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1020300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1930000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4114600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2823600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2986400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1492700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1697200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2152000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1479800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2182000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-865100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3134700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5858000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5394700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5721700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-774600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2578500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1665100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>483100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2859500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1936400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3010600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1649300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2879200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1963400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10196,130 +10428,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E96" s="3">
         <v>34700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>227100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>228800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>440400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>33000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>220700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>237400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>426300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>31100</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3">
         <v>579000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>44900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-188500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-187500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-742800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-42600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-125300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-147700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-602800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-37700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-669400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-46200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-26300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-649800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-46400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-561800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-22700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-578600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-8800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-8700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10440,8 +10676,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10562,8 +10801,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10684,370 +10926,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11131600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3796100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8377800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10442700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5641100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6148100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>363700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11794200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7039000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9645800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1992400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4585500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3521200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3845600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5649200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3501500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2381700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2307400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2084500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-244400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2973900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1078200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4299600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1932100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-820600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>526500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3681300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3189700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4001800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3109100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4360100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2673900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4038900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>425500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>822400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2334900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>4364300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1606700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1030700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1847400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>144000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-60000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>44100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>32600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-47400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>41500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-199900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>60300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>50300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-187700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>69800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>53000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>20900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>44500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>29200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-64300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>24900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>33100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>34100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-54800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>28800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-44400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-22800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-20400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3671800</v>
+      </c>
+      <c r="E102" s="3">
         <v>588100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5473600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5598700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2264800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2140500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2928800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6836500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-110800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>246100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-248300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1058000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2082000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3840200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5459500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4694100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1229800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-670800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>114000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1603300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1222300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>149100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-518400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-467900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1762300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-501200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1063600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2217100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-60100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-702600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1024500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1474800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>575300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>552000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>64300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>265800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-265100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>477300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-547600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>565700</v>
       </c>
     </row>
